--- a/resources/UserDetails_beta.xlsx
+++ b/resources/UserDetails_beta.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Email</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>JulissaRennerPhD@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrsDonyaSchoen@yopmail.com</t>
+  </si>
+  <si>
+    <t>RossieDuBuque@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1221,6 +1227,16 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/UserDetails_beta.xlsx
+++ b/resources/UserDetails_beta.xlsx
@@ -528,7 +528,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1217,47 +1217,47 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
